--- a/sample_data/output/excel/10_외식업물가_시군구별.xlsx
+++ b/sample_data/output/excel/10_외식업물가_시군구별.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,128 +511,6 @@
         <is>
           <t>전년동월대비변화율_count</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>26</v>
-      </c>
-      <c r="B2" t="n">
-        <v>45110</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>수원시</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>202501</v>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>26</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>45110</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19624.8</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2177</v>
-      </c>
-      <c r="M2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4498134.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>5</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.23182</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-0.05928</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>47</v>
-      </c>
-      <c r="B3" t="n">
-        <v>46110</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>수원시</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>202501</v>
-      </c>
-      <c r="E3" t="n">
-        <v>5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>47</v>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>46110</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>14903.4</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2643.2</v>
-      </c>
-      <c r="M3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3128582.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.009399999999999993</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.01188</v>
-      </c>
-      <c r="S3" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
